--- a/Outputs/Scenarios/PtX_demand_EL_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_EL_Electrification.xlsx
@@ -1555,7 +1555,7 @@
         <v>0.0001660964649254383</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03237137098182232</v>
+        <v>0.03237137098182231</v>
       </c>
     </row>
     <row r="31">
@@ -1568,7 +1568,7 @@
         <v>2050</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002043999629847512</v>
+        <v>0.002043999629847513</v>
       </c>
       <c r="D31" t="n">
         <v>0.0003902546717166335</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.005395228496970388</v>
+        <v>0.005395228496970387</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.03237137098182232</v>
+        <v>0.03237137098182231</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>8.741919206602016e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>0.005395228496970388</v>
+        <v>0.005395228496970387</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_EL_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_EL_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0001121986657946518</v>
       </c>
       <c r="K16" t="n">
-        <v>0.005510788683599053</v>
+        <v>0.006063910908582124</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0009184647805998423</v>
+        <v>0.001197028186601749</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.003673859122399369</v>
+        <v>0.004788112746406996</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.005510788683599053</v>
+        <v>0.004788112746406996</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>8.991622000807194e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0.007710163032090856</v>
+        <v>0.007569509979114698</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>5.442630688763226e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.07461530834200439</v>
+        <v>0.0732541346711781</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>1.61659285361267e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0009184647805998423</v>
+        <v>0.001197028186601749</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0001660964649254383</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03237137098182231</v>
+        <v>0.03265415515002822</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.005395228496970387</v>
+        <v>0.006445995779543875</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02158091398788155</v>
+        <v>0.0257839831181755</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.03237137098182231</v>
+        <v>0.0257839831181755</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>8.741919206602016e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>0.005395228496970387</v>
+        <v>0.006445995779543875</v>
       </c>
     </row>
     <row r="43">
